--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T10:56:37+00:00</t>
+    <t>2025-01-17T11:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T11:40:58+00:00</t>
+    <t>2025-01-21T12:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T12:24:15+00:00</t>
+    <t>2025-01-23T11:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:46:49+00:00</t>
+    <t>2025-01-24T11:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,13 +536,10 @@
     <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>The type of the specimen.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-probenmaterial</t>
   </si>
   <si>
     <t>.code</t>
@@ -791,6 +788,9 @@
     <t>A coded value specifying the technique that is used to perform the procedure.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>The  technique that is used to perform the procedure.</t>
   </si>
   <si>
@@ -844,9 +844,6 @@
   </si>
   <si>
     <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Codes describing the fasting status of the patient.</t>
@@ -2944,11 +2941,9 @@
       <c r="X14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -2981,21 +2976,21 @@
         <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3018,17 +3013,17 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3077,7 +3072,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3092,10 +3087,10 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3103,10 +3098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3129,13 +3124,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3186,7 +3181,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3201,21 +3196,21 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3238,16 +3233,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3297,7 +3292,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3312,7 +3307,7 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3323,10 +3318,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3349,16 +3344,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3408,7 +3403,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3423,21 +3418,21 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3460,13 +3455,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3517,7 +3512,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3532,21 +3527,21 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3569,13 +3564,13 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3626,7 +3621,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3641,7 +3636,7 @@
         <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -3652,10 +3647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3684,7 +3679,7 @@
         <v>131</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>133</v>
@@ -3737,7 +3732,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3752,7 +3747,7 @@
         <v>135</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -3763,14 +3758,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3792,10 +3787,10 @@
         <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>133</v>
@@ -3850,7 +3845,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3876,10 +3871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3902,13 +3897,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3959,7 +3954,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3974,21 +3969,21 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4011,13 +4006,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4068,7 +4063,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4083,21 +4078,21 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4120,13 +4115,13 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4177,7 +4172,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4195,7 +4190,7 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4203,10 +4198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4229,13 +4224,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4286,7 +4281,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4301,21 +4296,21 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4341,10 +4336,10 @@
         <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4371,7 +4366,7 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="Y27" t="s" s="2">
         <v>249</v>
@@ -4395,7 +4390,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4595,13 +4590,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y29" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4640,15 +4635,15 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4671,13 +4666,13 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4728,7 +4723,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4743,7 +4738,7 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -4754,10 +4749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4780,13 +4775,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4837,7 +4832,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4852,7 +4847,7 @@
         <v>76</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -4863,10 +4858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4895,7 +4890,7 @@
         <v>131</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>133</v>
@@ -4948,7 +4943,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4963,7 +4958,7 @@
         <v>135</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -4974,14 +4969,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5003,10 +4998,10 @@
         <v>130</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>133</v>
@@ -5061,7 +5056,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5087,10 +5082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5113,13 +5108,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5170,7 +5165,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5185,7 +5180,7 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5196,10 +5191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5225,10 +5220,10 @@
         <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5255,14 +5250,14 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
       </c>
@@ -5279,7 +5274,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5294,7 +5289,7 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5305,10 +5300,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5331,13 +5326,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5388,7 +5383,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5403,21 +5398,21 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5440,13 +5435,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5497,7 +5492,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5512,7 +5507,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5523,10 +5518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5549,13 +5544,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5606,7 +5601,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5621,7 +5616,7 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5632,10 +5627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5658,13 +5653,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5715,7 +5710,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5730,7 +5725,7 @@
         <v>76</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5741,10 +5736,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5773,7 +5768,7 @@
         <v>131</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>133</v>
@@ -5826,7 +5821,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5841,7 +5836,7 @@
         <v>135</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
@@ -5852,14 +5847,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5881,10 +5876,10 @@
         <v>130</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>133</v>
@@ -5939,7 +5934,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -5965,10 +5960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5994,10 +5989,10 @@
         <v>142</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6048,7 +6043,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6069,15 +6064,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6100,13 +6095,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6157,7 +6152,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6172,7 +6167,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6183,10 +6178,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6212,10 +6207,10 @@
         <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6242,14 +6237,14 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6266,7 +6261,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6281,21 +6276,21 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6318,13 +6313,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6375,7 +6370,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6390,21 +6385,21 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6427,13 +6422,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6484,7 +6479,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6499,21 +6494,21 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6536,13 +6531,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6569,14 +6564,14 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
       </c>
@@ -6593,7 +6588,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6608,21 +6603,21 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6648,16 +6643,16 @@
         <v>164</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6682,14 +6677,14 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
       </c>
@@ -6706,7 +6701,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6727,15 +6722,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6758,13 +6753,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6815,7 +6810,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6830,13 +6825,13 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
